--- a/diseases/d124/1995-1999.xlsx
+++ b/diseases/d124/1995-1999.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>2</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="S2" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1158,9 +1155,6 @@
       <c r="O4" t="n">
         <v>0</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="S4" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1551,9 +1545,6 @@
       <c r="O6" t="n">
         <v>2</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="S6" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1944,9 +1935,6 @@
       <c r="O8" t="n">
         <v>2</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="S8" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -2337,9 +2325,6 @@
       <c r="O10" t="n">
         <v>1</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="S10" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -2730,9 +2715,6 @@
       <c r="O12" t="n">
         <v>3</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="S12" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -3123,9 +3105,6 @@
       <c r="O14" t="n">
         <v>0</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="S14" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -3516,9 +3495,6 @@
       <c r="O16" t="n">
         <v>2</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="S16" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -3909,9 +3885,6 @@
       <c r="O18" t="n">
         <v>2</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="S18" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -4302,9 +4275,6 @@
       <c r="O20" t="n">
         <v>2</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="S20" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -4695,9 +4665,6 @@
       <c r="O22" t="n">
         <v>0</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="S22" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -5088,9 +5055,6 @@
       <c r="O24" t="n">
         <v>4</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="S24" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -5481,9 +5445,6 @@
       <c r="O26" t="n">
         <v>0</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="S26" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -5874,9 +5835,6 @@
       <c r="O28" t="n">
         <v>1</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="S28" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -6267,9 +6225,6 @@
       <c r="O30" t="n">
         <v>0</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="S30" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -6660,9 +6615,6 @@
       <c r="O32" t="n">
         <v>4</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="S32" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -7053,9 +7005,6 @@
       <c r="O34" t="n">
         <v>0</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="S34" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -7446,9 +7395,6 @@
       <c r="O36" t="n">
         <v>6</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="S36" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -7839,9 +7785,6 @@
       <c r="O38" t="n">
         <v>0</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="S38" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -8232,9 +8175,6 @@
       <c r="O40" t="n">
         <v>1</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="S40" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -8625,9 +8565,6 @@
       <c r="O42" t="n">
         <v>0</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="S42" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -9018,9 +8955,6 @@
       <c r="O44" t="n">
         <v>0</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="S44" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -9411,9 +9345,6 @@
       <c r="O46" t="n">
         <v>1</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="S46" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -9804,9 +9735,6 @@
       <c r="O48" t="n">
         <v>3</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="S48" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -10197,9 +10125,6 @@
       <c r="O50" t="n">
         <v>0</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="S50" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -10590,9 +10515,6 @@
       <c r="O52" t="n">
         <v>0</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="S52" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -10983,9 +10905,6 @@
       <c r="O54" t="n">
         <v>0</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="S54" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -11376,9 +11295,6 @@
       <c r="O56" t="n">
         <v>3</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="S56" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -11769,9 +11685,6 @@
       <c r="O58" t="n">
         <v>1</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="S58" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -12162,9 +12075,6 @@
       <c r="O60" t="n">
         <v>2</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="S60" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -12555,9 +12465,6 @@
       <c r="O62" t="n">
         <v>1</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="S62" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -12948,9 +12855,6 @@
       <c r="O64" t="n">
         <v>3</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="S64" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -13341,9 +13245,6 @@
       <c r="O66" t="n">
         <v>0</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="S66" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -13734,9 +13635,6 @@
       <c r="O68" t="n">
         <v>8</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="S68" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -14127,9 +14025,6 @@
       <c r="O70" t="n">
         <v>0</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="S70" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -14520,9 +14415,6 @@
       <c r="O72" t="n">
         <v>2</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="S72" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -14913,9 +14805,6 @@
       <c r="O74" t="n">
         <v>0</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="S74" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -15306,9 +15195,6 @@
       <c r="O76" t="n">
         <v>2</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="S76" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -15699,9 +15585,6 @@
       <c r="O78" t="n">
         <v>0</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="S78" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -16092,9 +15975,6 @@
       <c r="O80" t="n">
         <v>4</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="S80" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -16485,9 +16365,6 @@
       <c r="O82" t="n">
         <v>0</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="S82" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -16878,9 +16755,6 @@
       <c r="O84" t="n">
         <v>5</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="S84" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -17271,9 +17145,6 @@
       <c r="O86" t="n">
         <v>0</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="S86" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -17664,9 +17535,6 @@
       <c r="O88" t="n">
         <v>2</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="S88" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -18057,9 +17925,6 @@
       <c r="O90" t="n">
         <v>0</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="S90" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -18450,9 +18315,6 @@
       <c r="O92" t="n">
         <v>1</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="S92" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -18843,9 +18705,6 @@
       <c r="O94" t="n">
         <v>1</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="S94" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -19236,9 +19095,6 @@
       <c r="O96" t="n">
         <v>3</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="S96" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -19629,9 +19485,6 @@
       <c r="O98" t="n">
         <v>0</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="S98" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -20167,9 +20020,6 @@
       <c r="O101" t="n">
         <v>0</v>
       </c>
-      <c r="Q101" t="n">
-        <v>0</v>
-      </c>
       <c r="S101" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -20560,9 +20410,6 @@
       <c r="O103" t="n">
         <v>0</v>
       </c>
-      <c r="Q103" t="n">
-        <v>0</v>
-      </c>
       <c r="S103" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -21098,9 +20945,6 @@
       <c r="O106" t="n">
         <v>1</v>
       </c>
-      <c r="Q106" t="n">
-        <v>0</v>
-      </c>
       <c r="S106" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -21491,9 +21335,6 @@
       <c r="O108" t="n">
         <v>0</v>
       </c>
-      <c r="Q108" t="n">
-        <v>0</v>
-      </c>
       <c r="S108" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -22029,9 +21870,6 @@
       <c r="O111" t="n">
         <v>1</v>
       </c>
-      <c r="Q111" t="n">
-        <v>0</v>
-      </c>
       <c r="S111" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -22422,9 +22260,6 @@
       <c r="O113" t="n">
         <v>0</v>
       </c>
-      <c r="Q113" t="n">
-        <v>0</v>
-      </c>
       <c r="S113" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -22960,9 +22795,6 @@
       <c r="O116" t="n">
         <v>1</v>
       </c>
-      <c r="Q116" t="n">
-        <v>0</v>
-      </c>
       <c r="S116" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -23353,9 +23185,6 @@
       <c r="O118" t="n">
         <v>0</v>
       </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
       <c r="S118" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -23891,9 +23720,6 @@
       <c r="O121" t="n">
         <v>0</v>
       </c>
-      <c r="Q121" t="n">
-        <v>0</v>
-      </c>
       <c r="S121" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -24284,9 +24110,6 @@
       <c r="O123" t="n">
         <v>1</v>
       </c>
-      <c r="Q123" t="n">
-        <v>0</v>
-      </c>
       <c r="S123" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -24822,9 +24645,6 @@
       <c r="O126" t="n">
         <v>1</v>
       </c>
-      <c r="Q126" t="n">
-        <v>0</v>
-      </c>
       <c r="S126" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -25215,9 +25035,6 @@
       <c r="O128" t="n">
         <v>1</v>
       </c>
-      <c r="Q128" t="n">
-        <v>0</v>
-      </c>
       <c r="S128" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -25753,9 +25570,6 @@
       <c r="O131" t="n">
         <v>0</v>
       </c>
-      <c r="Q131" t="n">
-        <v>0</v>
-      </c>
       <c r="S131" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -26146,9 +25960,6 @@
       <c r="O133" t="n">
         <v>1</v>
       </c>
-      <c r="Q133" t="n">
-        <v>0</v>
-      </c>
       <c r="S133" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -26684,9 +26495,6 @@
       <c r="O136" t="n">
         <v>5</v>
       </c>
-      <c r="Q136" t="n">
-        <v>0</v>
-      </c>
       <c r="S136" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -27077,9 +26885,6 @@
       <c r="O138" t="n">
         <v>0</v>
       </c>
-      <c r="Q138" t="n">
-        <v>0</v>
-      </c>
       <c r="S138" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -27615,9 +27420,6 @@
       <c r="O141" t="n">
         <v>7</v>
       </c>
-      <c r="Q141" t="n">
-        <v>0</v>
-      </c>
       <c r="S141" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -28008,9 +27810,6 @@
       <c r="O143" t="n">
         <v>0</v>
       </c>
-      <c r="Q143" t="n">
-        <v>0</v>
-      </c>
       <c r="S143" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -28546,9 +28345,6 @@
       <c r="O146" t="n">
         <v>2</v>
       </c>
-      <c r="Q146" t="n">
-        <v>0</v>
-      </c>
       <c r="S146" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -28939,9 +28735,6 @@
       <c r="O148" t="n">
         <v>0</v>
       </c>
-      <c r="Q148" t="n">
-        <v>0</v>
-      </c>
       <c r="S148" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -29477,9 +29270,6 @@
       <c r="O151" t="n">
         <v>1</v>
       </c>
-      <c r="Q151" t="n">
-        <v>0</v>
-      </c>
       <c r="S151" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -29870,9 +29660,6 @@
       <c r="O153" t="n">
         <v>0</v>
       </c>
-      <c r="Q153" t="n">
-        <v>0</v>
-      </c>
       <c r="S153" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -30408,9 +30195,6 @@
       <c r="O156" t="n">
         <v>0</v>
       </c>
-      <c r="Q156" t="n">
-        <v>0</v>
-      </c>
       <c r="S156" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -30801,9 +30585,6 @@
       <c r="O158" t="n">
         <v>0</v>
       </c>
-      <c r="Q158" t="n">
-        <v>0</v>
-      </c>
       <c r="S158" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -31339,9 +31120,6 @@
       <c r="O161" t="n">
         <v>0</v>
       </c>
-      <c r="Q161" t="n">
-        <v>0</v>
-      </c>
       <c r="S161" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -31732,9 +31510,6 @@
       <c r="O163" t="n">
         <v>0</v>
       </c>
-      <c r="Q163" t="n">
-        <v>0</v>
-      </c>
       <c r="S163" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -32270,9 +32045,6 @@
       <c r="O166" t="n">
         <v>0</v>
       </c>
-      <c r="Q166" t="n">
-        <v>0</v>
-      </c>
       <c r="S166" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -32663,9 +32435,6 @@
       <c r="O168" t="n">
         <v>0</v>
       </c>
-      <c r="Q168" t="n">
-        <v>0</v>
-      </c>
       <c r="S168" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -33201,9 +32970,6 @@
       <c r="O171" t="n">
         <v>2</v>
       </c>
-      <c r="Q171" t="n">
-        <v>0</v>
-      </c>
       <c r="S171" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -33594,9 +33360,6 @@
       <c r="O173" t="n">
         <v>0</v>
       </c>
-      <c r="Q173" t="n">
-        <v>0</v>
-      </c>
       <c r="S173" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -34132,9 +33895,6 @@
       <c r="O176" t="n">
         <v>1</v>
       </c>
-      <c r="Q176" t="n">
-        <v>0</v>
-      </c>
       <c r="S176" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -34525,9 +34285,6 @@
       <c r="O178" t="n">
         <v>0</v>
       </c>
-      <c r="Q178" t="n">
-        <v>0</v>
-      </c>
       <c r="S178" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -35063,9 +34820,6 @@
       <c r="O181" t="n">
         <v>3</v>
       </c>
-      <c r="Q181" t="n">
-        <v>0</v>
-      </c>
       <c r="S181" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -35456,9 +35210,6 @@
       <c r="O183" t="n">
         <v>1</v>
       </c>
-      <c r="Q183" t="n">
-        <v>0</v>
-      </c>
       <c r="S183" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -35994,9 +35745,6 @@
       <c r="O186" t="n">
         <v>3</v>
       </c>
-      <c r="Q186" t="n">
-        <v>0</v>
-      </c>
       <c r="S186" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -36387,9 +36135,6 @@
       <c r="O188" t="n">
         <v>0</v>
       </c>
-      <c r="Q188" t="n">
-        <v>0</v>
-      </c>
       <c r="S188" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -36925,9 +36670,6 @@
       <c r="O191" t="n">
         <v>4</v>
       </c>
-      <c r="Q191" t="n">
-        <v>0</v>
-      </c>
       <c r="S191" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -37318,9 +37060,6 @@
       <c r="O193" t="n">
         <v>2</v>
       </c>
-      <c r="Q193" t="n">
-        <v>0</v>
-      </c>
       <c r="S193" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -37856,9 +37595,6 @@
       <c r="O196" t="n">
         <v>10</v>
       </c>
-      <c r="Q196" t="n">
-        <v>0</v>
-      </c>
       <c r="S196" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -38249,9 +37985,6 @@
       <c r="O198" t="n">
         <v>0</v>
       </c>
-      <c r="Q198" t="n">
-        <v>0</v>
-      </c>
       <c r="S198" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -38787,9 +38520,6 @@
       <c r="O201" t="n">
         <v>12</v>
       </c>
-      <c r="Q201" t="n">
-        <v>0</v>
-      </c>
       <c r="S201" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -39180,9 +38910,6 @@
       <c r="O203" t="n">
         <v>0</v>
       </c>
-      <c r="Q203" t="n">
-        <v>0</v>
-      </c>
       <c r="S203" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -39718,9 +39445,6 @@
       <c r="O206" t="n">
         <v>3</v>
       </c>
-      <c r="Q206" t="n">
-        <v>0</v>
-      </c>
       <c r="S206" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -40111,9 +39835,6 @@
       <c r="O208" t="n">
         <v>0</v>
       </c>
-      <c r="Q208" t="n">
-        <v>0</v>
-      </c>
       <c r="S208" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -40649,9 +40370,6 @@
       <c r="O211" t="n">
         <v>2</v>
       </c>
-      <c r="Q211" t="n">
-        <v>0</v>
-      </c>
       <c r="S211" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -41042,9 +40760,6 @@
       <c r="O213" t="n">
         <v>0</v>
       </c>
-      <c r="Q213" t="n">
-        <v>0</v>
-      </c>
       <c r="S213" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -41580,9 +41295,6 @@
       <c r="O216" t="n">
         <v>0</v>
       </c>
-      <c r="Q216" t="n">
-        <v>0</v>
-      </c>
       <c r="S216" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -41973,9 +41685,6 @@
       <c r="O218" t="n">
         <v>0</v>
       </c>
-      <c r="Q218" t="n">
-        <v>0</v>
-      </c>
       <c r="S218" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -42511,9 +42220,6 @@
       <c r="O221" t="n">
         <v>1</v>
       </c>
-      <c r="Q221" t="n">
-        <v>0</v>
-      </c>
       <c r="S221" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -42904,9 +42610,6 @@
       <c r="O223" t="n">
         <v>2</v>
       </c>
-      <c r="Q223" t="n">
-        <v>0</v>
-      </c>
       <c r="S223" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -43442,9 +43145,6 @@
       <c r="O226" t="n">
         <v>5</v>
       </c>
-      <c r="Q226" t="n">
-        <v>0</v>
-      </c>
       <c r="S226" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -43835,9 +43535,6 @@
       <c r="O228" t="n">
         <v>1</v>
       </c>
-      <c r="Q228" t="n">
-        <v>0</v>
-      </c>
       <c r="S228" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -44373,9 +44070,6 @@
       <c r="O231" t="n">
         <v>0</v>
       </c>
-      <c r="Q231" t="n">
-        <v>0</v>
-      </c>
       <c r="S231" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -44766,9 +44460,6 @@
       <c r="O233" t="n">
         <v>0</v>
       </c>
-      <c r="Q233" t="n">
-        <v>0</v>
-      </c>
       <c r="S233" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -45304,9 +44995,6 @@
       <c r="O236" t="n">
         <v>3</v>
       </c>
-      <c r="Q236" t="n">
-        <v>0</v>
-      </c>
       <c r="S236" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -45697,9 +45385,6 @@
       <c r="O238" t="n">
         <v>0</v>
       </c>
-      <c r="Q238" t="n">
-        <v>0</v>
-      </c>
       <c r="S238" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -46235,9 +45920,6 @@
       <c r="O241" t="n">
         <v>3</v>
       </c>
-      <c r="Q241" t="n">
-        <v>0</v>
-      </c>
       <c r="S241" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -46628,9 +46310,6 @@
       <c r="O243" t="n">
         <v>1</v>
       </c>
-      <c r="Q243" t="n">
-        <v>0</v>
-      </c>
       <c r="S243" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -47166,9 +46845,6 @@
       <c r="O246" t="n">
         <v>5</v>
       </c>
-      <c r="Q246" t="n">
-        <v>0</v>
-      </c>
       <c r="S246" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -47559,9 +47235,6 @@
       <c r="O248" t="n">
         <v>1</v>
       </c>
-      <c r="Q248" t="n">
-        <v>0</v>
-      </c>
       <c r="S248" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -48097,9 +47770,6 @@
       <c r="O251" t="n">
         <v>0</v>
       </c>
-      <c r="Q251" t="n">
-        <v>0</v>
-      </c>
       <c r="S251" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -48490,9 +48160,6 @@
       <c r="O253" t="n">
         <v>2</v>
       </c>
-      <c r="Q253" t="n">
-        <v>0</v>
-      </c>
       <c r="S253" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -49028,9 +48695,6 @@
       <c r="O256" t="n">
         <v>9</v>
       </c>
-      <c r="Q256" t="n">
-        <v>0</v>
-      </c>
       <c r="S256" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -49421,9 +49085,6 @@
       <c r="O258" t="n">
         <v>0</v>
       </c>
-      <c r="Q258" t="n">
-        <v>0</v>
-      </c>
       <c r="S258" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -49959,9 +49620,6 @@
       <c r="O261" t="n">
         <v>4</v>
       </c>
-      <c r="Q261" t="n">
-        <v>0</v>
-      </c>
       <c r="S261" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -50352,9 +50010,6 @@
       <c r="O263" t="n">
         <v>1</v>
       </c>
-      <c r="Q263" t="n">
-        <v>0</v>
-      </c>
       <c r="S263" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -50890,9 +50545,6 @@
       <c r="O266" t="n">
         <v>0</v>
       </c>
-      <c r="Q266" t="n">
-        <v>0</v>
-      </c>
       <c r="S266" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -51283,9 +50935,6 @@
       <c r="O268" t="n">
         <v>0</v>
       </c>
-      <c r="Q268" t="n">
-        <v>0</v>
-      </c>
       <c r="S268" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -51821,9 +51470,6 @@
       <c r="O271" t="n">
         <v>0</v>
       </c>
-      <c r="Q271" t="n">
-        <v>0</v>
-      </c>
       <c r="S271" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -52214,9 +51860,6 @@
       <c r="O273" t="n">
         <v>0</v>
       </c>
-      <c r="Q273" t="n">
-        <v>0</v>
-      </c>
       <c r="S273" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -52750,9 +52393,6 @@
         <v>0</v>
       </c>
       <c r="O276" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q276" t="n">
         <v>0</v>
       </c>
       <c r="S276" t="inlineStr">
